--- a/tables/describe.xlsx
+++ b/tables/describe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sarst\Documents\GitHub\group-info-sharing-study2\tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{826FEFD8-3E43-4299-B1F8-6759B213974F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3853D347-98C9-44B4-BA29-3B2939B3A6FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="960" yWindow="0" windowWidth="18300" windowHeight="15585" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="2190" windowWidth="20640" windowHeight="11040" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Describe" sheetId="1" r:id="rId1"/>
@@ -18,31 +18,19 @@
     <sheet name="Tabyl" sheetId="3" r:id="rId3"/>
     <sheet name="Purr" sheetId="4" r:id="rId4"/>
     <sheet name="Continuous Descriptives" sheetId="5" r:id="rId5"/>
-    <sheet name="Information Sharing" sheetId="6" r:id="rId6"/>
-    <sheet name="Coreelations" sheetId="7" r:id="rId7"/>
-    <sheet name="Control Descriptives" sheetId="8" r:id="rId8"/>
-    <sheet name="Control ANOVAs" sheetId="9" r:id="rId9"/>
-    <sheet name="Follow up" sheetId="10" r:id="rId10"/>
+    <sheet name="Info Sharing Top" sheetId="6" r:id="rId6"/>
+    <sheet name="Info Sharing Breakout" sheetId="7" r:id="rId7"/>
+    <sheet name="Coreelations" sheetId="8" r:id="rId8"/>
+    <sheet name="Control Descriptives" sheetId="9" r:id="rId9"/>
+    <sheet name="Control ANOVAs" sheetId="10" r:id="rId10"/>
+    <sheet name="Follow up" sheetId="11" r:id="rId11"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1651" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1686" uniqueCount="637">
   <si>
     <t>vars</t>
   </si>
@@ -1013,6 +1001,96 @@
     <t>1.04</t>
   </si>
   <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Share M (SD)</t>
+  </si>
+  <si>
+    <t>Withhold M (SD)</t>
+  </si>
+  <si>
+    <t>Distort M (SD)</t>
+  </si>
+  <si>
+    <t>Overall</t>
+  </si>
+  <si>
+    <t>Combined</t>
+  </si>
+  <si>
+    <t>0.63 (0.25)</t>
+  </si>
+  <si>
+    <t>0.25 (0.18)</t>
+  </si>
+  <si>
+    <t>0.12 (0.13)</t>
+  </si>
+  <si>
+    <t>Structure</t>
+  </si>
+  <si>
+    <t>Intergroup</t>
+  </si>
+  <si>
+    <t>0.63 (0.23)</t>
+  </si>
+  <si>
+    <t>0.26 (0.18)</t>
+  </si>
+  <si>
+    <t>0.11 (0.12)</t>
+  </si>
+  <si>
+    <t>Interindividual</t>
+  </si>
+  <si>
+    <t>0.63 (0.27)</t>
+  </si>
+  <si>
+    <t>0.25 (0.19)</t>
+  </si>
+  <si>
+    <t>0.12 (0.14)</t>
+  </si>
+  <si>
+    <t>Motivation</t>
+  </si>
+  <si>
+    <t>Proself</t>
+  </si>
+  <si>
+    <t>0.54 (0.23)</t>
+  </si>
+  <si>
+    <t>0.30 (0.18)</t>
+  </si>
+  <si>
+    <t>0.16 (0.13)</t>
+  </si>
+  <si>
+    <t>Hybrid</t>
+  </si>
+  <si>
+    <t>0.66 (0.24)</t>
+  </si>
+  <si>
+    <t>0.24 (0.18)</t>
+  </si>
+  <si>
+    <t>0.10 (0.12)</t>
+  </si>
+  <si>
+    <t>Prosocial</t>
+  </si>
+  <si>
+    <t>0.69 (0.25)</t>
+  </si>
+  <si>
+    <t>0.21 (0.19)</t>
+  </si>
+  <si>
     <t>condition</t>
   </si>
   <si>
@@ -1268,9 +1346,6 @@
     <t>0.19 (0.22)</t>
   </si>
   <si>
-    <t>Structure</t>
-  </si>
-  <si>
     <t>Motivation: Prosocial</t>
   </si>
   <si>
@@ -1304,159 +1379,162 @@
     <t>4. Common, Low</t>
   </si>
   <si>
+    <t>-0.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.09</t>
+  </si>
+  <si>
+    <t>5. Common, High</t>
+  </si>
+  <si>
     <t>-0.02</t>
   </si>
   <si>
+    <t xml:space="preserve"> 0.15*</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.43*</t>
+  </si>
+  <si>
+    <t>6. Unique, Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.68*</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.31*</t>
+  </si>
+  <si>
+    <t>7. Unique, High</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 0.01</t>
   </si>
   <si>
-    <t xml:space="preserve"> 0.07</t>
-  </si>
-  <si>
-    <t>5. Common, High</t>
+    <t xml:space="preserve"> 0.22*</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.04</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.51*</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.08</t>
+  </si>
+  <si>
+    <t>Cooperation</t>
+  </si>
+  <si>
+    <t>8. Self-Reported Cooperation</t>
+  </si>
+  <si>
+    <t>-0.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.32*</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.13*</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.52*</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.18*</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.62*</t>
+  </si>
+  <si>
+    <t>Controls</t>
+  </si>
+  <si>
+    <t>9. Age</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.16*</t>
+  </si>
+  <si>
+    <t>-0.08</t>
+  </si>
+  <si>
+    <t>-0.04</t>
+  </si>
+  <si>
+    <t>10. Sex</t>
+  </si>
+  <si>
+    <t>-0.19*</t>
+  </si>
+  <si>
+    <t>-0.05</t>
   </si>
   <si>
     <t>-0.01</t>
   </si>
   <si>
-    <t xml:space="preserve"> 0.15*</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.32*</t>
-  </si>
-  <si>
-    <t>6. Unique, Low</t>
+    <t>-0.10</t>
+  </si>
+  <si>
+    <t>11. Need for Cognition</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.19*</t>
+  </si>
+  <si>
+    <t>12. Narcissism</t>
+  </si>
+  <si>
+    <t>-0.07</t>
   </si>
   <si>
     <t xml:space="preserve"> 0.05</t>
   </si>
   <si>
+    <t>-0.21*</t>
+  </si>
+  <si>
+    <t>13. Psychopathy</t>
+  </si>
+  <si>
+    <t>-0.09</t>
+  </si>
+  <si>
+    <t>-0.12</t>
+  </si>
+  <si>
+    <t>-0.14*</t>
+  </si>
+  <si>
+    <t>-0.22*</t>
+  </si>
+  <si>
+    <t>-0.15*</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 0.50*</t>
+  </si>
+  <si>
+    <t>14. Machiavellianism</t>
+  </si>
+  <si>
+    <t>-0.23*</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 0.63*</t>
   </si>
   <si>
-    <t xml:space="preserve"> 0.27*</t>
-  </si>
-  <si>
-    <t>7. Unique, High</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.22*</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.53*</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.06</t>
-  </si>
-  <si>
-    <t>Cooperation</t>
-  </si>
-  <si>
-    <t>8. Self-Reported Cooperation</t>
-  </si>
-  <si>
-    <t>-0.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.33*</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.52*</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.18*</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.64*</t>
-  </si>
-  <si>
-    <t>Controls</t>
-  </si>
-  <si>
-    <t>9. Age</t>
-  </si>
-  <si>
-    <t>-0.07</t>
-  </si>
-  <si>
-    <t>-0.05</t>
-  </si>
-  <si>
-    <t>10. Sex</t>
-  </si>
-  <si>
-    <t>-0.19*</t>
-  </si>
-  <si>
-    <t>-0.08</t>
-  </si>
-  <si>
-    <t>-0.03</t>
-  </si>
-  <si>
-    <t>-0.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.09</t>
-  </si>
-  <si>
-    <t>11. Need for Cognition</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.17*</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.02</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.04</t>
-  </si>
-  <si>
-    <t>12. Narcissism</t>
-  </si>
-  <si>
-    <t>-0.21*</t>
-  </si>
-  <si>
-    <t>13. Psychopathy</t>
-  </si>
-  <si>
-    <t>-0.14*</t>
-  </si>
-  <si>
-    <t>-0.23*</t>
-  </si>
-  <si>
-    <t>-0.16*</t>
-  </si>
-  <si>
-    <t>-0.15*</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.50*</t>
-  </si>
-  <si>
-    <t>14. Machiavellianism</t>
-  </si>
-  <si>
-    <t>-0.09</t>
-  </si>
-  <si>
-    <t>-0.25*</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.65*</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 0.69*</t>
-  </si>
-  <si>
     <t>Interindividual_Proself</t>
   </si>
   <si>
@@ -1610,9 +1688,6 @@
     <t>0.02</t>
   </si>
   <si>
-    <t>Motivation</t>
-  </si>
-  <si>
     <t>0.57</t>
   </si>
   <si>
@@ -1866,9 +1941,6 @@
   </si>
   <si>
     <t>[-2.39, 1.14]</t>
-  </si>
-  <si>
-    <t>order</t>
   </si>
 </sst>
 </file>
@@ -1946,17 +2018,32 @@
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Table10" displayName="Table10" ref="A1:H10" totalsRowShown="0">
-  <autoFilter ref="A1:H10" xr:uid="{00000000-0009-0000-0100-00000A000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{00000000-000C-0000-FFFF-FFFF09000000}" name="Table10" displayName="Table10" ref="A1:F19" totalsRowShown="0">
+  <autoFilter ref="A1:F19" xr:uid="{00000000-0009-0000-0100-00000A000000}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="Control Variable"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="Effect"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="df"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="F"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="p"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="ηp²"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{00000000-000C-0000-FFFF-FFFF0A000000}" name="Table11" displayName="Table11" ref="A1:H10" totalsRowShown="0">
+  <autoFilter ref="A1:H10" xr:uid="{00000000-0009-0000-0100-00000B000000}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0900-000001000000}" name="Variable"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0900-000002000000}" name="Comparison"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0900-000003000000}" name="Estimate"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0900-000004000000}" name="SE"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0900-000005000000}" name="df"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0900-000006000000}" name="t"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0900-000007000000}" name="CI"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0900-000008000000}" name="p"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0A00-000001000000}" name="Variable"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0A00-000002000000}" name="Comparison"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0A00-000003000000}" name="Estimate"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0A00-000004000000}" name="SE"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0A00-000005000000}" name="df"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0A00-000006000000}" name="t"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0A00-000007000000}" name="CI"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0A00-000008000000}" name="p"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1999,13 +2086,9 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Table5" displayName="Table5" ref="A1:E6" totalsRowShown="0">
-  <autoFilter ref="A1:E6" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E6">
-    <sortCondition ref="A1:A6"/>
-  </sortState>
-  <tableColumns count="5">
-    <tableColumn id="5" xr3:uid="{65CFED6E-C95F-4FED-B002-D225D1A06CD5}" name="order"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Table5" displayName="Table5" ref="A1:D6" totalsRowShown="0">
+  <autoFilter ref="A1:D6" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+  <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Variable"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="n"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="M"/>
@@ -2016,70 +2099,70 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Table6" displayName="Table6" ref="A1:F31" totalsRowShown="0">
-  <autoFilter ref="A1:F31" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Table6" displayName="Table6" ref="A1:F9" totalsRowShown="0">
+  <autoFilter ref="A1:F9" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="condition"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Information Type"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Level"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Group"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="n"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Share"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Withhold"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Distort"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Share M (SD)"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Withhold M (SD)"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Distort M (SD)"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Table7" displayName="Table7" ref="A1:O19" totalsRowShown="0">
-  <autoFilter ref="A1:O19" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
-  <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Variable"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Structure"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Motivation: Prosocial"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Motivation: Hybrid"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="Common, Low"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="Common, High"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="Unique, Low"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0600-000008000000}" name="Unique, High"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0600-000009000000}" name="Self-Reported Cooperation"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0600-00000A000000}" name="Age"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0600-00000B000000}" name="Sex"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0600-00000C000000}" name="Need for Cognition"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0600-00000D000000}" name="Narcissism"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0600-00000E000000}" name="Psychopathy"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0600-00000F000000}" name="Machiavellianism"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Table7" displayName="Table7" ref="A1:F31" totalsRowShown="0">
+  <autoFilter ref="A1:F31" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="condition"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Information Type"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="n"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Share"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="Withhold"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="Distort"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Table8" displayName="Table8" ref="A1:G7" totalsRowShown="0">
-  <autoFilter ref="A1:G7" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
-  <tableColumns count="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Table8" displayName="Table8" ref="A1:O19" totalsRowShown="0">
+  <autoFilter ref="A1:O19" xr:uid="{00000000-0009-0000-0100-000008000000}"/>
+  <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="Variable"/>
-    <tableColumn id="8" xr3:uid="{22C6A003-3525-443D-9C56-4C96AAE2D1E2}" name="Interindividual_Prosocial"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Interindividual_Hybrid"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Interindividual_Proself"/>
-    <tableColumn id="9" xr3:uid="{EA3FEFDF-DA29-413D-A16B-9D3A19BDAF61}" name="Intergroup_Prosocial"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="Intergroup_Hybrid"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="Intergroup_Proself"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Structure"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Motivation: Prosocial"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Motivation: Hybrid"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="Common, Low"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="Common, High"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="Unique, Low"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0700-000008000000}" name="Unique, High"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0700-000009000000}" name="Self-Reported Cooperation"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0700-00000A000000}" name="Age"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0700-00000B000000}" name="Sex"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0700-00000C000000}" name="Need for Cognition"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0700-00000D000000}" name="Narcissism"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0700-00000E000000}" name="Psychopathy"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0700-00000F000000}" name="Machiavellianism"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Table9" displayName="Table9" ref="A1:F19" totalsRowShown="0">
-  <autoFilter ref="A1:F19" xr:uid="{00000000-0009-0000-0100-000009000000}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="Control Variable"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="Effect"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="df"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="F"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="p"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="ηp²"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Table9" displayName="Table9" ref="A1:G7" totalsRowShown="0">
+  <autoFilter ref="A1:G7" xr:uid="{00000000-0009-0000-0100-000009000000}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="Variable"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="Interindividual_Proself"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="Interindividual_Hybrid"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="Interindividual_Prosocial"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0800-000005000000}" name="Intergroup_Proself"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0800-000006000000}" name="Intergroup_Hybrid"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0800-000007000000}" name="Intergroup_Prosocial"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3155,6 +3238,401 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>543</v>
+      </c>
+      <c r="B1" t="s">
+        <v>544</v>
+      </c>
+      <c r="C1" t="s">
+        <v>545</v>
+      </c>
+      <c r="D1" t="s">
+        <v>546</v>
+      </c>
+      <c r="E1" t="s">
+        <v>547</v>
+      </c>
+      <c r="F1" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>332</v>
+      </c>
+      <c r="C2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D2" t="s">
+        <v>549</v>
+      </c>
+      <c r="E2" t="s">
+        <v>550</v>
+      </c>
+      <c r="F2" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>341</v>
+      </c>
+      <c r="C3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D3" t="s">
+        <v>552</v>
+      </c>
+      <c r="E3" t="s">
+        <v>553</v>
+      </c>
+      <c r="F3" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>555</v>
+      </c>
+      <c r="C4" t="s">
+        <v>277</v>
+      </c>
+      <c r="D4" t="s">
+        <v>556</v>
+      </c>
+      <c r="E4" t="s">
+        <v>557</v>
+      </c>
+      <c r="F4" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>513</v>
+      </c>
+      <c r="B5" t="s">
+        <v>332</v>
+      </c>
+      <c r="C5" t="s">
+        <v>278</v>
+      </c>
+      <c r="D5" t="s">
+        <v>559</v>
+      </c>
+      <c r="E5" t="s">
+        <v>560</v>
+      </c>
+      <c r="F5" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>513</v>
+      </c>
+      <c r="B6" t="s">
+        <v>341</v>
+      </c>
+      <c r="C6" t="s">
+        <v>277</v>
+      </c>
+      <c r="D6" t="s">
+        <v>562</v>
+      </c>
+      <c r="E6" t="s">
+        <v>563</v>
+      </c>
+      <c r="F6" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>513</v>
+      </c>
+      <c r="B7" t="s">
+        <v>555</v>
+      </c>
+      <c r="C7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D7" t="s">
+        <v>564</v>
+      </c>
+      <c r="E7" t="s">
+        <v>565</v>
+      </c>
+      <c r="F7" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>308</v>
+      </c>
+      <c r="B8" t="s">
+        <v>332</v>
+      </c>
+      <c r="C8" t="s">
+        <v>278</v>
+      </c>
+      <c r="D8" t="s">
+        <v>558</v>
+      </c>
+      <c r="E8" t="s">
+        <v>566</v>
+      </c>
+      <c r="F8" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>308</v>
+      </c>
+      <c r="B9" t="s">
+        <v>341</v>
+      </c>
+      <c r="C9" t="s">
+        <v>277</v>
+      </c>
+      <c r="D9" t="s">
+        <v>568</v>
+      </c>
+      <c r="E9" t="s">
+        <v>569</v>
+      </c>
+      <c r="F9" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>308</v>
+      </c>
+      <c r="B10" t="s">
+        <v>555</v>
+      </c>
+      <c r="C10" t="s">
+        <v>277</v>
+      </c>
+      <c r="D10" t="s">
+        <v>570</v>
+      </c>
+      <c r="E10" t="s">
+        <v>571</v>
+      </c>
+      <c r="F10" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>311</v>
+      </c>
+      <c r="B11" t="s">
+        <v>332</v>
+      </c>
+      <c r="C11" t="s">
+        <v>278</v>
+      </c>
+      <c r="D11" t="s">
+        <v>572</v>
+      </c>
+      <c r="E11" t="s">
+        <v>573</v>
+      </c>
+      <c r="F11" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>311</v>
+      </c>
+      <c r="B12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C12" t="s">
+        <v>277</v>
+      </c>
+      <c r="D12" t="s">
+        <v>574</v>
+      </c>
+      <c r="E12" t="s">
+        <v>575</v>
+      </c>
+      <c r="F12" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>311</v>
+      </c>
+      <c r="B13" t="s">
+        <v>555</v>
+      </c>
+      <c r="C13" t="s">
+        <v>277</v>
+      </c>
+      <c r="D13" t="s">
+        <v>576</v>
+      </c>
+      <c r="E13" t="s">
+        <v>577</v>
+      </c>
+      <c r="F13" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>314</v>
+      </c>
+      <c r="B14" t="s">
+        <v>332</v>
+      </c>
+      <c r="C14" t="s">
+        <v>278</v>
+      </c>
+      <c r="D14" t="s">
+        <v>574</v>
+      </c>
+      <c r="E14" t="s">
+        <v>578</v>
+      </c>
+      <c r="F14" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>314</v>
+      </c>
+      <c r="B15" t="s">
+        <v>341</v>
+      </c>
+      <c r="C15" t="s">
+        <v>277</v>
+      </c>
+      <c r="D15" t="s">
+        <v>579</v>
+      </c>
+      <c r="E15" t="s">
+        <v>580</v>
+      </c>
+      <c r="F15" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>314</v>
+      </c>
+      <c r="B16" t="s">
+        <v>555</v>
+      </c>
+      <c r="C16" t="s">
+        <v>277</v>
+      </c>
+      <c r="D16" t="s">
+        <v>581</v>
+      </c>
+      <c r="E16" t="s">
+        <v>582</v>
+      </c>
+      <c r="F16" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>317</v>
+      </c>
+      <c r="B17" t="s">
+        <v>332</v>
+      </c>
+      <c r="C17" t="s">
+        <v>278</v>
+      </c>
+      <c r="D17" t="s">
+        <v>583</v>
+      </c>
+      <c r="E17" t="s">
+        <v>577</v>
+      </c>
+      <c r="F17" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>317</v>
+      </c>
+      <c r="B18" t="s">
+        <v>341</v>
+      </c>
+      <c r="C18" t="s">
+        <v>277</v>
+      </c>
+      <c r="D18" t="s">
+        <v>584</v>
+      </c>
+      <c r="E18" t="s">
+        <v>585</v>
+      </c>
+      <c r="F18" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>317</v>
+      </c>
+      <c r="B19" t="s">
+        <v>555</v>
+      </c>
+      <c r="C19" t="s">
+        <v>277</v>
+      </c>
+      <c r="D19" t="s">
+        <v>586</v>
+      </c>
+      <c r="E19" t="s">
+        <v>571</v>
+      </c>
+      <c r="F19" t="s">
+        <v>551</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions gridLines="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -3163,25 +3641,25 @@
         <v>240</v>
       </c>
       <c r="B1" t="s">
-        <v>558</v>
+        <v>587</v>
       </c>
       <c r="C1" t="s">
-        <v>559</v>
+        <v>588</v>
       </c>
       <c r="D1" t="s">
-        <v>560</v>
+        <v>589</v>
       </c>
       <c r="E1" t="s">
-        <v>515</v>
+        <v>545</v>
       </c>
       <c r="F1" t="s">
-        <v>561</v>
+        <v>590</v>
       </c>
       <c r="G1" t="s">
-        <v>562</v>
+        <v>591</v>
       </c>
       <c r="H1" t="s">
-        <v>517</v>
+        <v>547</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -3189,25 +3667,25 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>563</v>
+        <v>592</v>
       </c>
       <c r="C2" t="s">
-        <v>564</v>
+        <v>593</v>
       </c>
       <c r="D2" t="s">
-        <v>565</v>
+        <v>594</v>
       </c>
       <c r="E2">
         <v>221</v>
       </c>
       <c r="F2" t="s">
-        <v>566</v>
+        <v>595</v>
       </c>
       <c r="G2" t="s">
-        <v>567</v>
+        <v>596</v>
       </c>
       <c r="H2" t="s">
-        <v>568</v>
+        <v>597</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -3215,25 +3693,25 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>569</v>
+        <v>598</v>
       </c>
       <c r="C3" t="s">
-        <v>450</v>
+        <v>478</v>
       </c>
       <c r="D3" t="s">
-        <v>570</v>
+        <v>599</v>
       </c>
       <c r="E3">
         <v>221</v>
       </c>
       <c r="F3" t="s">
-        <v>571</v>
+        <v>600</v>
       </c>
       <c r="G3" t="s">
-        <v>572</v>
+        <v>601</v>
       </c>
       <c r="H3" t="s">
-        <v>573</v>
+        <v>602</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -3241,25 +3719,25 @@
         <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>574</v>
+        <v>603</v>
       </c>
       <c r="C4" t="s">
-        <v>575</v>
+        <v>604</v>
       </c>
       <c r="D4" t="s">
-        <v>565</v>
+        <v>594</v>
       </c>
       <c r="E4">
         <v>221</v>
       </c>
       <c r="F4" t="s">
-        <v>576</v>
+        <v>605</v>
       </c>
       <c r="G4" t="s">
-        <v>577</v>
+        <v>606</v>
       </c>
       <c r="H4" t="s">
-        <v>578</v>
+        <v>607</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -3267,25 +3745,25 @@
         <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>579</v>
+        <v>608</v>
       </c>
       <c r="C5" t="s">
-        <v>580</v>
+        <v>609</v>
       </c>
       <c r="D5" t="s">
-        <v>581</v>
+        <v>610</v>
       </c>
       <c r="E5">
         <v>221</v>
       </c>
       <c r="F5" t="s">
-        <v>582</v>
+        <v>611</v>
       </c>
       <c r="G5" t="s">
-        <v>583</v>
+        <v>612</v>
       </c>
       <c r="H5" t="s">
-        <v>584</v>
+        <v>613</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -3293,25 +3771,25 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>585</v>
+        <v>614</v>
       </c>
       <c r="C6" t="s">
-        <v>586</v>
+        <v>615</v>
       </c>
       <c r="D6" t="s">
-        <v>587</v>
+        <v>616</v>
       </c>
       <c r="E6">
         <v>221</v>
       </c>
       <c r="F6" t="s">
-        <v>588</v>
+        <v>617</v>
       </c>
       <c r="G6" t="s">
-        <v>589</v>
+        <v>618</v>
       </c>
       <c r="H6" t="s">
-        <v>590</v>
+        <v>619</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -3319,25 +3797,25 @@
         <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>591</v>
+        <v>620</v>
       </c>
       <c r="C7" t="s">
-        <v>592</v>
+        <v>621</v>
       </c>
       <c r="D7" t="s">
-        <v>565</v>
+        <v>594</v>
       </c>
       <c r="E7">
         <v>221</v>
       </c>
       <c r="F7" t="s">
-        <v>593</v>
+        <v>622</v>
       </c>
       <c r="G7" t="s">
-        <v>594</v>
+        <v>623</v>
       </c>
       <c r="H7" t="s">
-        <v>595</v>
+        <v>624</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -3345,10 +3823,10 @@
         <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>596</v>
+        <v>625</v>
       </c>
       <c r="C8" t="s">
-        <v>597</v>
+        <v>626</v>
       </c>
       <c r="D8" t="s">
         <v>310</v>
@@ -3357,13 +3835,13 @@
         <v>221</v>
       </c>
       <c r="F8" t="s">
-        <v>598</v>
+        <v>627</v>
       </c>
       <c r="G8" t="s">
-        <v>599</v>
+        <v>628</v>
       </c>
       <c r="H8" t="s">
-        <v>556</v>
+        <v>585</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -3371,10 +3849,10 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>600</v>
+        <v>629</v>
       </c>
       <c r="C9" t="s">
-        <v>601</v>
+        <v>630</v>
       </c>
       <c r="D9" t="s">
         <v>310</v>
@@ -3383,13 +3861,13 @@
         <v>221</v>
       </c>
       <c r="F9" t="s">
-        <v>602</v>
+        <v>631</v>
       </c>
       <c r="G9" t="s">
-        <v>603</v>
+        <v>632</v>
       </c>
       <c r="H9" t="s">
-        <v>556</v>
+        <v>585</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -3397,25 +3875,25 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>604</v>
+        <v>633</v>
       </c>
       <c r="C10" t="s">
-        <v>605</v>
+        <v>634</v>
       </c>
       <c r="D10" t="s">
-        <v>570</v>
+        <v>599</v>
       </c>
       <c r="E10">
         <v>221</v>
       </c>
       <c r="F10" t="s">
-        <v>606</v>
+        <v>635</v>
       </c>
       <c r="G10" t="s">
-        <v>607</v>
+        <v>636</v>
       </c>
       <c r="H10" t="s">
-        <v>556</v>
+        <v>585</v>
       </c>
     </row>
   </sheetData>
@@ -3430,14 +3908,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H198"/>
+  <dimension ref="A1:B198"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="31.140625" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -3445,7 +3919,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -3453,7 +3927,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -3461,7 +3935,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -3469,7 +3943,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -3477,7 +3951,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -3485,7 +3959,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>23</v>
       </c>
@@ -3493,7 +3967,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -3501,7 +3975,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -3509,7 +3983,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -3517,7 +3991,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -3525,19 +3999,15 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
       <c r="B12" t="s">
         <v>33</v>
       </c>
-      <c r="H12" t="e">
-        <f>SUM(#REF!)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>34</v>
       </c>
@@ -3545,7 +4015,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>36</v>
       </c>
@@ -3553,7 +4023,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -3561,7 +4031,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -3569,7 +4039,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -3577,7 +4047,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>43</v>
       </c>
@@ -3585,7 +4055,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -3593,7 +4063,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>47</v>
       </c>
@@ -3601,7 +4071,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>49</v>
       </c>
@@ -3609,19 +4079,15 @@
         <v>48</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>50</v>
       </c>
       <c r="B22" t="s">
         <v>48</v>
       </c>
-      <c r="H22" t="e">
-        <f>SUM(#REF!)</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>51</v>
       </c>
@@ -3629,7 +4095,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>52</v>
       </c>
@@ -3637,7 +4103,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>54</v>
       </c>
@@ -3645,7 +4111,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>55</v>
       </c>
@@ -3653,7 +4119,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>56</v>
       </c>
@@ -3661,7 +4127,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>57</v>
       </c>
@@ -3669,7 +4135,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>59</v>
       </c>
@@ -3677,7 +4143,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>61</v>
       </c>
@@ -3685,7 +4151,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>41</v>
       </c>
@@ -3693,7 +4159,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>43</v>
       </c>
@@ -5043,10 +5509,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D197"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="33" customWidth="1"/>
-    <col min="2" max="2" width="37" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -8394,113 +8856,91 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="4" width="10" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>608</v>
+        <v>240</v>
       </c>
       <c r="B1" t="s">
-        <v>240</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>306</v>
       </c>
       <c r="D1" t="s">
-        <v>306</v>
-      </c>
-      <c r="E1" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B2">
+        <v>229</v>
+      </c>
+      <c r="C2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D2" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>311</v>
+      </c>
+      <c r="B3">
+        <v>228</v>
+      </c>
+      <c r="C3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D3" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>314</v>
+      </c>
+      <c r="B4">
+        <v>228</v>
+      </c>
+      <c r="C4" t="s">
+        <v>315</v>
+      </c>
+      <c r="D4" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>317</v>
+      </c>
+      <c r="B5">
+        <v>228</v>
+      </c>
+      <c r="C5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D5" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>320</v>
       </c>
-      <c r="C2">
+      <c r="B6">
         <v>228</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C6" t="s">
         <v>321</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D6" t="s">
         <v>322</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C3">
-        <v>229</v>
-      </c>
-      <c r="D3" t="s">
-        <v>309</v>
-      </c>
-      <c r="E3" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>311</v>
-      </c>
-      <c r="C4">
-        <v>228</v>
-      </c>
-      <c r="D4" t="s">
-        <v>312</v>
-      </c>
-      <c r="E4" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>314</v>
-      </c>
-      <c r="C5">
-        <v>228</v>
-      </c>
-      <c r="D5" t="s">
-        <v>315</v>
-      </c>
-      <c r="E5" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>317</v>
-      </c>
-      <c r="C6">
-        <v>228</v>
-      </c>
-      <c r="D6" t="s">
-        <v>318</v>
-      </c>
-      <c r="E6" t="s">
-        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -8515,13 +8955,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="6" width="14.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -8529,150 +8966,110 @@
         <v>323</v>
       </c>
       <c r="B1" t="s">
+        <v>239</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
         <v>324</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>325</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>326</v>
-      </c>
-      <c r="F1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B2" t="s">
         <v>328</v>
       </c>
-      <c r="C2" t="s">
-        <v>249</v>
+      <c r="C2">
+        <v>230</v>
       </c>
       <c r="D2" t="s">
-        <v>249</v>
+        <v>329</v>
       </c>
       <c r="E2" t="s">
-        <v>249</v>
+        <v>330</v>
       </c>
       <c r="F2" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>328</v>
-      </c>
-      <c r="B3" t="s">
-        <v>329</v>
-      </c>
-      <c r="C3" t="s">
-        <v>330</v>
-      </c>
-      <c r="D3" t="s">
         <v>331</v>
-      </c>
-      <c r="E3" t="s">
-        <v>332</v>
-      </c>
-      <c r="F3" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B4" t="s">
+        <v>333</v>
+      </c>
+      <c r="C4">
+        <v>110</v>
+      </c>
+      <c r="D4" t="s">
         <v>334</v>
       </c>
-      <c r="C4" t="s">
-        <v>330</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>335</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>336</v>
-      </c>
-      <c r="F4" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B5" t="s">
+        <v>337</v>
+      </c>
+      <c r="C5">
+        <v>120</v>
+      </c>
+      <c r="D5" t="s">
         <v>338</v>
       </c>
-      <c r="C5" t="s">
-        <v>330</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>339</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>340</v>
-      </c>
-      <c r="F5" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>328</v>
-      </c>
-      <c r="B6" t="s">
-        <v>342</v>
-      </c>
-      <c r="C6" t="s">
-        <v>330</v>
-      </c>
-      <c r="D6" t="s">
-        <v>343</v>
-      </c>
-      <c r="E6" t="s">
-        <v>344</v>
-      </c>
-      <c r="F6" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B7" t="s">
-        <v>346</v>
-      </c>
-      <c r="C7" t="s">
-        <v>249</v>
+        <v>342</v>
+      </c>
+      <c r="C7">
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>249</v>
+        <v>343</v>
       </c>
       <c r="E7" t="s">
-        <v>249</v>
+        <v>344</v>
       </c>
       <c r="F7" t="s">
-        <v>249</v>
+        <v>345</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>341</v>
+      </c>
+      <c r="B8" t="s">
         <v>346</v>
       </c>
-      <c r="B8" t="s">
-        <v>329</v>
-      </c>
-      <c r="C8" t="s">
-        <v>297</v>
+      <c r="C8">
+        <v>76</v>
       </c>
       <c r="D8" t="s">
         <v>347</v>
@@ -8686,462 +9083,22 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B9" t="s">
-        <v>334</v>
-      </c>
-      <c r="C9" t="s">
-        <v>297</v>
+        <v>350</v>
+      </c>
+      <c r="C9">
+        <v>77</v>
       </c>
       <c r="D9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F9" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>346</v>
-      </c>
-      <c r="B10" t="s">
-        <v>338</v>
-      </c>
-      <c r="C10" t="s">
-        <v>297</v>
-      </c>
-      <c r="D10" t="s">
-        <v>353</v>
-      </c>
-      <c r="E10" t="s">
-        <v>354</v>
-      </c>
-      <c r="F10" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>346</v>
-      </c>
-      <c r="B11" t="s">
-        <v>342</v>
-      </c>
-      <c r="C11" t="s">
-        <v>297</v>
-      </c>
-      <c r="D11" t="s">
-        <v>356</v>
-      </c>
-      <c r="E11" t="s">
-        <v>357</v>
-      </c>
-      <c r="F11" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>359</v>
-      </c>
-      <c r="B12" t="s">
-        <v>359</v>
-      </c>
-      <c r="C12" t="s">
-        <v>249</v>
-      </c>
-      <c r="D12" t="s">
-        <v>249</v>
-      </c>
-      <c r="E12" t="s">
-        <v>249</v>
-      </c>
-      <c r="F12" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>359</v>
-      </c>
-      <c r="B13" t="s">
-        <v>329</v>
-      </c>
-      <c r="C13" t="s">
-        <v>281</v>
-      </c>
-      <c r="D13" t="s">
-        <v>360</v>
-      </c>
-      <c r="E13" t="s">
-        <v>361</v>
-      </c>
-      <c r="F13" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>359</v>
-      </c>
-      <c r="B14" t="s">
-        <v>334</v>
-      </c>
-      <c r="C14" t="s">
-        <v>281</v>
-      </c>
-      <c r="D14" t="s">
-        <v>363</v>
-      </c>
-      <c r="E14" t="s">
-        <v>364</v>
-      </c>
-      <c r="F14" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>359</v>
-      </c>
-      <c r="B15" t="s">
-        <v>338</v>
-      </c>
-      <c r="C15" t="s">
-        <v>281</v>
-      </c>
-      <c r="D15" t="s">
-        <v>366</v>
-      </c>
-      <c r="E15" t="s">
-        <v>367</v>
-      </c>
-      <c r="F15" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>359</v>
-      </c>
-      <c r="B16" t="s">
-        <v>342</v>
-      </c>
-      <c r="C16" t="s">
-        <v>281</v>
-      </c>
-      <c r="D16" t="s">
-        <v>368</v>
-      </c>
-      <c r="E16" t="s">
-        <v>369</v>
-      </c>
-      <c r="F16" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>371</v>
-      </c>
-      <c r="B17" t="s">
-        <v>371</v>
-      </c>
-      <c r="C17" t="s">
-        <v>249</v>
-      </c>
-      <c r="D17" t="s">
-        <v>249</v>
-      </c>
-      <c r="E17" t="s">
-        <v>249</v>
-      </c>
-      <c r="F17" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>371</v>
-      </c>
-      <c r="B18" t="s">
-        <v>329</v>
-      </c>
-      <c r="C18" t="s">
-        <v>372</v>
-      </c>
-      <c r="D18" t="s">
-        <v>373</v>
-      </c>
-      <c r="E18" t="s">
-        <v>374</v>
-      </c>
-      <c r="F18" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>371</v>
-      </c>
-      <c r="B19" t="s">
-        <v>334</v>
-      </c>
-      <c r="C19" t="s">
-        <v>372</v>
-      </c>
-      <c r="D19" t="s">
-        <v>376</v>
-      </c>
-      <c r="E19" t="s">
-        <v>377</v>
-      </c>
-      <c r="F19" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>371</v>
-      </c>
-      <c r="B20" t="s">
-        <v>338</v>
-      </c>
-      <c r="C20" t="s">
-        <v>372</v>
-      </c>
-      <c r="D20" t="s">
-        <v>379</v>
-      </c>
-      <c r="E20" t="s">
-        <v>361</v>
-      </c>
-      <c r="F20" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>371</v>
-      </c>
-      <c r="B21" t="s">
-        <v>342</v>
-      </c>
-      <c r="C21" t="s">
-        <v>372</v>
-      </c>
-      <c r="D21" t="s">
-        <v>381</v>
-      </c>
-      <c r="E21" t="s">
-        <v>382</v>
-      </c>
-      <c r="F21" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>384</v>
-      </c>
-      <c r="B22" t="s">
-        <v>384</v>
-      </c>
-      <c r="C22" t="s">
-        <v>249</v>
-      </c>
-      <c r="D22" t="s">
-        <v>249</v>
-      </c>
-      <c r="E22" t="s">
-        <v>249</v>
-      </c>
-      <c r="F22" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>384</v>
-      </c>
-      <c r="B23" t="s">
-        <v>329</v>
-      </c>
-      <c r="C23" t="s">
-        <v>297</v>
-      </c>
-      <c r="D23" t="s">
-        <v>385</v>
-      </c>
-      <c r="E23" t="s">
-        <v>386</v>
-      </c>
-      <c r="F23" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>384</v>
-      </c>
-      <c r="B24" t="s">
-        <v>334</v>
-      </c>
-      <c r="C24" t="s">
-        <v>297</v>
-      </c>
-      <c r="D24" t="s">
-        <v>388</v>
-      </c>
-      <c r="E24" t="s">
-        <v>389</v>
-      </c>
-      <c r="F24" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>384</v>
-      </c>
-      <c r="B25" t="s">
-        <v>338</v>
-      </c>
-      <c r="C25" t="s">
-        <v>297</v>
-      </c>
-      <c r="D25" t="s">
-        <v>391</v>
-      </c>
-      <c r="E25" t="s">
-        <v>392</v>
-      </c>
-      <c r="F25" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>384</v>
-      </c>
-      <c r="B26" t="s">
-        <v>342</v>
-      </c>
-      <c r="C26" t="s">
-        <v>297</v>
-      </c>
-      <c r="D26" t="s">
-        <v>393</v>
-      </c>
-      <c r="E26" t="s">
-        <v>394</v>
-      </c>
-      <c r="F26" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>396</v>
-      </c>
-      <c r="B27" t="s">
-        <v>396</v>
-      </c>
-      <c r="C27" t="s">
-        <v>249</v>
-      </c>
-      <c r="D27" t="s">
-        <v>249</v>
-      </c>
-      <c r="E27" t="s">
-        <v>249</v>
-      </c>
-      <c r="F27" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>396</v>
-      </c>
-      <c r="B28" t="s">
-        <v>329</v>
-      </c>
-      <c r="C28" t="s">
-        <v>291</v>
-      </c>
-      <c r="D28" t="s">
-        <v>397</v>
-      </c>
-      <c r="E28" t="s">
-        <v>398</v>
-      </c>
-      <c r="F28" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>396</v>
-      </c>
-      <c r="B29" t="s">
-        <v>334</v>
-      </c>
-      <c r="C29" t="s">
-        <v>291</v>
-      </c>
-      <c r="D29" t="s">
-        <v>400</v>
-      </c>
-      <c r="E29" t="s">
-        <v>401</v>
-      </c>
-      <c r="F29" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>396</v>
-      </c>
-      <c r="B30" t="s">
-        <v>338</v>
-      </c>
-      <c r="C30" t="s">
-        <v>291</v>
-      </c>
-      <c r="D30" t="s">
-        <v>403</v>
-      </c>
-      <c r="E30" t="s">
-        <v>404</v>
-      </c>
-      <c r="F30" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>396</v>
-      </c>
-      <c r="B31" t="s">
-        <v>342</v>
-      </c>
-      <c r="C31" t="s">
-        <v>291</v>
-      </c>
-      <c r="D31" t="s">
-        <v>405</v>
-      </c>
-      <c r="E31" t="s">
-        <v>406</v>
-      </c>
-      <c r="F31" t="s">
-        <v>407</v>
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -9156,903 +9113,627 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="26.5703125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>240</v>
+        <v>353</v>
       </c>
       <c r="B1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>355</v>
+      </c>
+      <c r="E1" t="s">
+        <v>356</v>
+      </c>
+      <c r="F1" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C3" t="s">
+        <v>360</v>
+      </c>
+      <c r="D3" t="s">
+        <v>361</v>
+      </c>
+      <c r="E3" t="s">
+        <v>362</v>
+      </c>
+      <c r="F3" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>358</v>
+      </c>
+      <c r="B4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C4" t="s">
+        <v>360</v>
+      </c>
+      <c r="D4" t="s">
+        <v>365</v>
+      </c>
+      <c r="E4" t="s">
+        <v>366</v>
+      </c>
+      <c r="F4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>358</v>
+      </c>
+      <c r="B5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C5" t="s">
+        <v>360</v>
+      </c>
+      <c r="D5" t="s">
+        <v>369</v>
+      </c>
+      <c r="E5" t="s">
+        <v>370</v>
+      </c>
+      <c r="F5" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>358</v>
+      </c>
+      <c r="B6" t="s">
+        <v>372</v>
+      </c>
+      <c r="C6" t="s">
+        <v>360</v>
+      </c>
+      <c r="D6" t="s">
+        <v>373</v>
+      </c>
+      <c r="E6" t="s">
+        <v>374</v>
+      </c>
+      <c r="F6" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>376</v>
+      </c>
+      <c r="B7" t="s">
+        <v>376</v>
+      </c>
+      <c r="C7" t="s">
+        <v>249</v>
+      </c>
+      <c r="D7" t="s">
+        <v>249</v>
+      </c>
+      <c r="E7" t="s">
+        <v>249</v>
+      </c>
+      <c r="F7" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>376</v>
+      </c>
+      <c r="B8" t="s">
+        <v>359</v>
+      </c>
+      <c r="C8" t="s">
+        <v>297</v>
+      </c>
+      <c r="D8" t="s">
+        <v>377</v>
+      </c>
+      <c r="E8" t="s">
+        <v>378</v>
+      </c>
+      <c r="F8" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>376</v>
+      </c>
+      <c r="B9" t="s">
+        <v>364</v>
+      </c>
+      <c r="C9" t="s">
+        <v>297</v>
+      </c>
+      <c r="D9" t="s">
+        <v>380</v>
+      </c>
+      <c r="E9" t="s">
+        <v>381</v>
+      </c>
+      <c r="F9" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>376</v>
+      </c>
+      <c r="B10" t="s">
+        <v>368</v>
+      </c>
+      <c r="C10" t="s">
+        <v>297</v>
+      </c>
+      <c r="D10" t="s">
+        <v>383</v>
+      </c>
+      <c r="E10" t="s">
+        <v>384</v>
+      </c>
+      <c r="F10" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>376</v>
+      </c>
+      <c r="B11" t="s">
+        <v>372</v>
+      </c>
+      <c r="C11" t="s">
+        <v>297</v>
+      </c>
+      <c r="D11" t="s">
+        <v>386</v>
+      </c>
+      <c r="E11" t="s">
+        <v>387</v>
+      </c>
+      <c r="F11" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>389</v>
+      </c>
+      <c r="B12" t="s">
+        <v>389</v>
+      </c>
+      <c r="C12" t="s">
+        <v>249</v>
+      </c>
+      <c r="D12" t="s">
+        <v>249</v>
+      </c>
+      <c r="E12" t="s">
+        <v>249</v>
+      </c>
+      <c r="F12" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>389</v>
+      </c>
+      <c r="B13" t="s">
+        <v>359</v>
+      </c>
+      <c r="C13" t="s">
+        <v>281</v>
+      </c>
+      <c r="D13" t="s">
+        <v>390</v>
+      </c>
+      <c r="E13" t="s">
+        <v>391</v>
+      </c>
+      <c r="F13" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>389</v>
+      </c>
+      <c r="B14" t="s">
+        <v>364</v>
+      </c>
+      <c r="C14" t="s">
+        <v>281</v>
+      </c>
+      <c r="D14" t="s">
+        <v>393</v>
+      </c>
+      <c r="E14" t="s">
+        <v>394</v>
+      </c>
+      <c r="F14" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>389</v>
+      </c>
+      <c r="B15" t="s">
+        <v>368</v>
+      </c>
+      <c r="C15" t="s">
+        <v>281</v>
+      </c>
+      <c r="D15" t="s">
+        <v>396</v>
+      </c>
+      <c r="E15" t="s">
+        <v>397</v>
+      </c>
+      <c r="F15" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>389</v>
+      </c>
+      <c r="B16" t="s">
+        <v>372</v>
+      </c>
+      <c r="C16" t="s">
+        <v>281</v>
+      </c>
+      <c r="D16" t="s">
+        <v>398</v>
+      </c>
+      <c r="E16" t="s">
+        <v>399</v>
+      </c>
+      <c r="F16" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>401</v>
+      </c>
+      <c r="B17" t="s">
+        <v>401</v>
+      </c>
+      <c r="C17" t="s">
+        <v>249</v>
+      </c>
+      <c r="D17" t="s">
+        <v>249</v>
+      </c>
+      <c r="E17" t="s">
+        <v>249</v>
+      </c>
+      <c r="F17" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>401</v>
+      </c>
+      <c r="B18" t="s">
+        <v>359</v>
+      </c>
+      <c r="C18" t="s">
+        <v>402</v>
+      </c>
+      <c r="D18" t="s">
+        <v>403</v>
+      </c>
+      <c r="E18" t="s">
+        <v>404</v>
+      </c>
+      <c r="F18" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>401</v>
+      </c>
+      <c r="B19" t="s">
+        <v>364</v>
+      </c>
+      <c r="C19" t="s">
+        <v>402</v>
+      </c>
+      <c r="D19" t="s">
+        <v>406</v>
+      </c>
+      <c r="E19" t="s">
+        <v>407</v>
+      </c>
+      <c r="F19" t="s">
         <v>408</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>401</v>
+      </c>
+      <c r="B20" t="s">
+        <v>368</v>
+      </c>
+      <c r="C20" t="s">
+        <v>402</v>
+      </c>
+      <c r="D20" t="s">
         <v>409</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E20" t="s">
+        <v>391</v>
+      </c>
+      <c r="F20" t="s">
         <v>410</v>
       </c>
-      <c r="E1" t="s">
-        <v>329</v>
-      </c>
-      <c r="F1" t="s">
-        <v>334</v>
-      </c>
-      <c r="G1" t="s">
-        <v>338</v>
-      </c>
-      <c r="H1" t="s">
-        <v>342</v>
-      </c>
-      <c r="I1" t="s">
-        <v>320</v>
-      </c>
-      <c r="J1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L1" t="s">
-        <v>308</v>
-      </c>
-      <c r="M1" t="s">
-        <v>311</v>
-      </c>
-      <c r="N1" t="s">
-        <v>314</v>
-      </c>
-      <c r="O1" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>401</v>
+      </c>
+      <c r="B21" t="s">
+        <v>372</v>
+      </c>
+      <c r="C21" t="s">
+        <v>402</v>
+      </c>
+      <c r="D21" t="s">
         <v>411</v>
       </c>
-      <c r="B2" t="s">
-        <v>249</v>
-      </c>
-      <c r="C2" t="s">
-        <v>249</v>
-      </c>
-      <c r="D2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E2" t="s">
-        <v>249</v>
-      </c>
-      <c r="F2" t="s">
-        <v>249</v>
-      </c>
-      <c r="G2" t="s">
-        <v>249</v>
-      </c>
-      <c r="H2" t="s">
-        <v>249</v>
-      </c>
-      <c r="I2" t="s">
-        <v>249</v>
-      </c>
-      <c r="J2" t="s">
-        <v>249</v>
-      </c>
-      <c r="K2" t="s">
-        <v>249</v>
-      </c>
-      <c r="L2" t="s">
-        <v>249</v>
-      </c>
-      <c r="M2" t="s">
-        <v>249</v>
-      </c>
-      <c r="N2" t="s">
-        <v>249</v>
-      </c>
-      <c r="O2" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="E21" t="s">
         <v>412</v>
       </c>
-      <c r="B3" t="s">
-        <v>249</v>
-      </c>
-      <c r="C3" t="s">
-        <v>249</v>
-      </c>
-      <c r="D3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E3" t="s">
-        <v>249</v>
-      </c>
-      <c r="F3" t="s">
-        <v>249</v>
-      </c>
-      <c r="G3" t="s">
-        <v>249</v>
-      </c>
-      <c r="H3" t="s">
-        <v>249</v>
-      </c>
-      <c r="I3" t="s">
-        <v>249</v>
-      </c>
-      <c r="J3" t="s">
-        <v>249</v>
-      </c>
-      <c r="K3" t="s">
-        <v>249</v>
-      </c>
-      <c r="L3" t="s">
-        <v>249</v>
-      </c>
-      <c r="M3" t="s">
-        <v>249</v>
-      </c>
-      <c r="N3" t="s">
-        <v>249</v>
-      </c>
-      <c r="O3" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="F21" t="s">
         <v>413</v>
       </c>
-      <c r="B4" t="s">
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>414</v>
       </c>
-      <c r="C4" t="s">
-        <v>249</v>
-      </c>
-      <c r="D4" t="s">
-        <v>249</v>
-      </c>
-      <c r="E4" t="s">
-        <v>249</v>
-      </c>
-      <c r="F4" t="s">
-        <v>249</v>
-      </c>
-      <c r="G4" t="s">
-        <v>249</v>
-      </c>
-      <c r="H4" t="s">
-        <v>249</v>
-      </c>
-      <c r="I4" t="s">
-        <v>249</v>
-      </c>
-      <c r="J4" t="s">
-        <v>249</v>
-      </c>
-      <c r="K4" t="s">
-        <v>249</v>
-      </c>
-      <c r="L4" t="s">
-        <v>249</v>
-      </c>
-      <c r="M4" t="s">
-        <v>249</v>
-      </c>
-      <c r="N4" t="s">
-        <v>249</v>
-      </c>
-      <c r="O4" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B22" t="s">
+        <v>414</v>
+      </c>
+      <c r="C22" t="s">
+        <v>249</v>
+      </c>
+      <c r="D22" t="s">
+        <v>249</v>
+      </c>
+      <c r="E22" t="s">
+        <v>249</v>
+      </c>
+      <c r="F22" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>414</v>
+      </c>
+      <c r="B23" t="s">
+        <v>359</v>
+      </c>
+      <c r="C23" t="s">
+        <v>297</v>
+      </c>
+      <c r="D23" t="s">
         <v>415</v>
       </c>
-      <c r="B5" t="s">
+      <c r="E23" t="s">
         <v>416</v>
       </c>
-      <c r="C5" t="s">
+      <c r="F23" t="s">
         <v>417</v>
       </c>
-      <c r="D5" t="s">
-        <v>249</v>
-      </c>
-      <c r="E5" t="s">
-        <v>249</v>
-      </c>
-      <c r="F5" t="s">
-        <v>249</v>
-      </c>
-      <c r="G5" t="s">
-        <v>249</v>
-      </c>
-      <c r="H5" t="s">
-        <v>249</v>
-      </c>
-      <c r="I5" t="s">
-        <v>249</v>
-      </c>
-      <c r="J5" t="s">
-        <v>249</v>
-      </c>
-      <c r="K5" t="s">
-        <v>249</v>
-      </c>
-      <c r="L5" t="s">
-        <v>249</v>
-      </c>
-      <c r="M5" t="s">
-        <v>249</v>
-      </c>
-      <c r="N5" t="s">
-        <v>249</v>
-      </c>
-      <c r="O5" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>414</v>
+      </c>
+      <c r="B24" t="s">
+        <v>364</v>
+      </c>
+      <c r="C24" t="s">
+        <v>297</v>
+      </c>
+      <c r="D24" t="s">
         <v>418</v>
       </c>
-      <c r="B6" t="s">
-        <v>249</v>
-      </c>
-      <c r="C6" t="s">
-        <v>249</v>
-      </c>
-      <c r="D6" t="s">
-        <v>249</v>
-      </c>
-      <c r="E6" t="s">
-        <v>249</v>
-      </c>
-      <c r="F6" t="s">
-        <v>249</v>
-      </c>
-      <c r="G6" t="s">
-        <v>249</v>
-      </c>
-      <c r="H6" t="s">
-        <v>249</v>
-      </c>
-      <c r="I6" t="s">
-        <v>249</v>
-      </c>
-      <c r="J6" t="s">
-        <v>249</v>
-      </c>
-      <c r="K6" t="s">
-        <v>249</v>
-      </c>
-      <c r="L6" t="s">
-        <v>249</v>
-      </c>
-      <c r="M6" t="s">
-        <v>249</v>
-      </c>
-      <c r="N6" t="s">
-        <v>249</v>
-      </c>
-      <c r="O6" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="E24" t="s">
         <v>419</v>
       </c>
-      <c r="B7" t="s">
+      <c r="F24" t="s">
         <v>420</v>
       </c>
-      <c r="C7" t="s">
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>414</v>
+      </c>
+      <c r="B25" t="s">
+        <v>368</v>
+      </c>
+      <c r="C25" t="s">
+        <v>297</v>
+      </c>
+      <c r="D25" t="s">
         <v>421</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E25" t="s">
         <v>422</v>
       </c>
-      <c r="E7" t="s">
-        <v>249</v>
-      </c>
-      <c r="F7" t="s">
-        <v>249</v>
-      </c>
-      <c r="G7" t="s">
-        <v>249</v>
-      </c>
-      <c r="H7" t="s">
-        <v>249</v>
-      </c>
-      <c r="I7" t="s">
-        <v>249</v>
-      </c>
-      <c r="J7" t="s">
-        <v>249</v>
-      </c>
-      <c r="K7" t="s">
-        <v>249</v>
-      </c>
-      <c r="L7" t="s">
-        <v>249</v>
-      </c>
-      <c r="M7" t="s">
-        <v>249</v>
-      </c>
-      <c r="N7" t="s">
-        <v>249</v>
-      </c>
-      <c r="O7" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="F25" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>414</v>
+      </c>
+      <c r="B26" t="s">
+        <v>372</v>
+      </c>
+      <c r="C26" t="s">
+        <v>297</v>
+      </c>
+      <c r="D26" t="s">
         <v>423</v>
       </c>
-      <c r="B8" t="s">
+      <c r="E26" t="s">
         <v>424</v>
       </c>
-      <c r="C8" t="s">
+      <c r="F26" t="s">
         <v>425</v>
       </c>
-      <c r="D8" t="s">
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>426</v>
       </c>
-      <c r="E8" t="s">
+      <c r="B27" t="s">
+        <v>426</v>
+      </c>
+      <c r="C27" t="s">
+        <v>249</v>
+      </c>
+      <c r="D27" t="s">
+        <v>249</v>
+      </c>
+      <c r="E27" t="s">
+        <v>249</v>
+      </c>
+      <c r="F27" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>426</v>
+      </c>
+      <c r="B28" t="s">
+        <v>359</v>
+      </c>
+      <c r="C28" t="s">
+        <v>291</v>
+      </c>
+      <c r="D28" t="s">
         <v>427</v>
       </c>
-      <c r="F8" t="s">
-        <v>249</v>
-      </c>
-      <c r="G8" t="s">
-        <v>249</v>
-      </c>
-      <c r="H8" t="s">
-        <v>249</v>
-      </c>
-      <c r="I8" t="s">
-        <v>249</v>
-      </c>
-      <c r="J8" t="s">
-        <v>249</v>
-      </c>
-      <c r="K8" t="s">
-        <v>249</v>
-      </c>
-      <c r="L8" t="s">
-        <v>249</v>
-      </c>
-      <c r="M8" t="s">
-        <v>249</v>
-      </c>
-      <c r="N8" t="s">
-        <v>249</v>
-      </c>
-      <c r="O8" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="E28" t="s">
         <v>428</v>
       </c>
-      <c r="B9" t="s">
-        <v>421</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="F28" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>426</v>
       </c>
-      <c r="D9" t="s">
-        <v>429</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="B29" t="s">
+        <v>364</v>
+      </c>
+      <c r="C29" t="s">
+        <v>291</v>
+      </c>
+      <c r="D29" t="s">
         <v>430</v>
       </c>
-      <c r="F9" t="s">
+      <c r="E29" t="s">
         <v>431</v>
       </c>
-      <c r="G9" t="s">
-        <v>249</v>
-      </c>
-      <c r="H9" t="s">
-        <v>249</v>
-      </c>
-      <c r="I9" t="s">
-        <v>249</v>
-      </c>
-      <c r="J9" t="s">
-        <v>249</v>
-      </c>
-      <c r="K9" t="s">
-        <v>249</v>
-      </c>
-      <c r="L9" t="s">
-        <v>249</v>
-      </c>
-      <c r="M9" t="s">
-        <v>249</v>
-      </c>
-      <c r="N9" t="s">
-        <v>249</v>
-      </c>
-      <c r="O9" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="F29" t="s">
         <v>432</v>
       </c>
-      <c r="B10" t="s">
-        <v>421</v>
-      </c>
-      <c r="C10" t="s">
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>426</v>
+      </c>
+      <c r="B30" t="s">
+        <v>368</v>
+      </c>
+      <c r="C30" t="s">
+        <v>291</v>
+      </c>
+      <c r="D30" t="s">
         <v>433</v>
       </c>
-      <c r="D10" t="s">
-        <v>414</v>
-      </c>
-      <c r="E10" t="s">
-        <v>414</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="E30" t="s">
         <v>434</v>
       </c>
-      <c r="G10" t="s">
+      <c r="F30" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>426</v>
+      </c>
+      <c r="B31" t="s">
+        <v>372</v>
+      </c>
+      <c r="C31" t="s">
+        <v>291</v>
+      </c>
+      <c r="D31" t="s">
         <v>435</v>
       </c>
-      <c r="H10" t="s">
-        <v>249</v>
-      </c>
-      <c r="I10" t="s">
-        <v>249</v>
-      </c>
-      <c r="J10" t="s">
-        <v>249</v>
-      </c>
-      <c r="K10" t="s">
-        <v>249</v>
-      </c>
-      <c r="L10" t="s">
-        <v>249</v>
-      </c>
-      <c r="M10" t="s">
-        <v>249</v>
-      </c>
-      <c r="N10" t="s">
-        <v>249</v>
-      </c>
-      <c r="O10" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="E31" t="s">
         <v>436</v>
       </c>
-      <c r="B11" t="s">
-        <v>249</v>
-      </c>
-      <c r="C11" t="s">
-        <v>249</v>
-      </c>
-      <c r="D11" t="s">
-        <v>249</v>
-      </c>
-      <c r="E11" t="s">
-        <v>249</v>
-      </c>
-      <c r="F11" t="s">
-        <v>249</v>
-      </c>
-      <c r="G11" t="s">
-        <v>249</v>
-      </c>
-      <c r="H11" t="s">
-        <v>249</v>
-      </c>
-      <c r="I11" t="s">
-        <v>249</v>
-      </c>
-      <c r="J11" t="s">
-        <v>249</v>
-      </c>
-      <c r="K11" t="s">
-        <v>249</v>
-      </c>
-      <c r="L11" t="s">
-        <v>249</v>
-      </c>
-      <c r="M11" t="s">
-        <v>249</v>
-      </c>
-      <c r="N11" t="s">
-        <v>249</v>
-      </c>
-      <c r="O11" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="F31" t="s">
         <v>437</v>
-      </c>
-      <c r="B12" t="s">
-        <v>438</v>
-      </c>
-      <c r="C12" t="s">
-        <v>439</v>
-      </c>
-      <c r="D12" t="s">
-        <v>421</v>
-      </c>
-      <c r="E12" t="s">
-        <v>440</v>
-      </c>
-      <c r="F12" t="s">
-        <v>441</v>
-      </c>
-      <c r="G12" t="s">
-        <v>442</v>
-      </c>
-      <c r="H12" t="s">
-        <v>443</v>
-      </c>
-      <c r="I12" t="s">
-        <v>249</v>
-      </c>
-      <c r="J12" t="s">
-        <v>249</v>
-      </c>
-      <c r="K12" t="s">
-        <v>249</v>
-      </c>
-      <c r="L12" t="s">
-        <v>249</v>
-      </c>
-      <c r="M12" t="s">
-        <v>249</v>
-      </c>
-      <c r="N12" t="s">
-        <v>249</v>
-      </c>
-      <c r="O12" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>444</v>
-      </c>
-      <c r="B13" t="s">
-        <v>249</v>
-      </c>
-      <c r="C13" t="s">
-        <v>249</v>
-      </c>
-      <c r="D13" t="s">
-        <v>249</v>
-      </c>
-      <c r="E13" t="s">
-        <v>249</v>
-      </c>
-      <c r="F13" t="s">
-        <v>249</v>
-      </c>
-      <c r="G13" t="s">
-        <v>249</v>
-      </c>
-      <c r="H13" t="s">
-        <v>249</v>
-      </c>
-      <c r="I13" t="s">
-        <v>249</v>
-      </c>
-      <c r="J13" t="s">
-        <v>249</v>
-      </c>
-      <c r="K13" t="s">
-        <v>249</v>
-      </c>
-      <c r="L13" t="s">
-        <v>249</v>
-      </c>
-      <c r="M13" t="s">
-        <v>249</v>
-      </c>
-      <c r="N13" t="s">
-        <v>249</v>
-      </c>
-      <c r="O13" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>445</v>
-      </c>
-      <c r="B14" t="s">
-        <v>425</v>
-      </c>
-      <c r="C14" t="s">
-        <v>446</v>
-      </c>
-      <c r="D14" t="s">
-        <v>435</v>
-      </c>
-      <c r="E14" t="s">
-        <v>421</v>
-      </c>
-      <c r="F14" t="s">
-        <v>416</v>
-      </c>
-      <c r="G14" t="s">
-        <v>435</v>
-      </c>
-      <c r="H14" t="s">
-        <v>429</v>
-      </c>
-      <c r="I14" t="s">
-        <v>447</v>
-      </c>
-      <c r="J14" t="s">
-        <v>249</v>
-      </c>
-      <c r="K14" t="s">
-        <v>249</v>
-      </c>
-      <c r="L14" t="s">
-        <v>249</v>
-      </c>
-      <c r="M14" t="s">
-        <v>249</v>
-      </c>
-      <c r="N14" t="s">
-        <v>249</v>
-      </c>
-      <c r="O14" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>448</v>
-      </c>
-      <c r="B15" t="s">
-        <v>449</v>
-      </c>
-      <c r="C15" t="s">
-        <v>447</v>
-      </c>
-      <c r="D15" t="s">
-        <v>450</v>
-      </c>
-      <c r="E15" t="s">
-        <v>451</v>
-      </c>
-      <c r="F15" t="s">
-        <v>452</v>
-      </c>
-      <c r="G15" t="s">
-        <v>421</v>
-      </c>
-      <c r="H15" t="s">
-        <v>438</v>
-      </c>
-      <c r="I15" t="s">
-        <v>424</v>
-      </c>
-      <c r="J15" t="s">
-        <v>453</v>
-      </c>
-      <c r="K15" t="s">
-        <v>249</v>
-      </c>
-      <c r="L15" t="s">
-        <v>249</v>
-      </c>
-      <c r="M15" t="s">
-        <v>249</v>
-      </c>
-      <c r="N15" t="s">
-        <v>249</v>
-      </c>
-      <c r="O15" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>454</v>
-      </c>
-      <c r="B16" t="s">
-        <v>424</v>
-      </c>
-      <c r="C16" t="s">
-        <v>422</v>
-      </c>
-      <c r="D16" t="s">
-        <v>414</v>
-      </c>
-      <c r="E16" t="s">
-        <v>455</v>
-      </c>
-      <c r="F16" t="s">
-        <v>422</v>
-      </c>
-      <c r="G16" t="s">
-        <v>442</v>
-      </c>
-      <c r="H16" t="s">
-        <v>456</v>
-      </c>
-      <c r="I16" t="s">
-        <v>457</v>
-      </c>
-      <c r="J16" t="s">
-        <v>456</v>
-      </c>
-      <c r="K16" t="s">
-        <v>452</v>
-      </c>
-      <c r="L16" t="s">
-        <v>249</v>
-      </c>
-      <c r="M16" t="s">
-        <v>249</v>
-      </c>
-      <c r="N16" t="s">
-        <v>249</v>
-      </c>
-      <c r="O16" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>458</v>
-      </c>
-      <c r="B17" t="s">
-        <v>446</v>
-      </c>
-      <c r="C17" t="s">
-        <v>429</v>
-      </c>
-      <c r="D17" t="s">
-        <v>438</v>
-      </c>
-      <c r="E17" t="s">
-        <v>421</v>
-      </c>
-      <c r="F17" t="s">
-        <v>422</v>
-      </c>
-      <c r="G17" t="s">
-        <v>421</v>
-      </c>
-      <c r="H17" t="s">
-        <v>424</v>
-      </c>
-      <c r="I17" t="s">
-        <v>452</v>
-      </c>
-      <c r="J17" t="s">
-        <v>459</v>
-      </c>
-      <c r="K17" t="s">
-        <v>447</v>
-      </c>
-      <c r="L17" t="s">
-        <v>438</v>
-      </c>
-      <c r="M17" t="s">
-        <v>249</v>
-      </c>
-      <c r="N17" t="s">
-        <v>249</v>
-      </c>
-      <c r="O17" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>460</v>
-      </c>
-      <c r="B18" t="s">
-        <v>447</v>
-      </c>
-      <c r="C18" t="s">
-        <v>457</v>
-      </c>
-      <c r="D18" t="s">
-        <v>438</v>
-      </c>
-      <c r="E18" t="s">
-        <v>447</v>
-      </c>
-      <c r="F18" t="s">
-        <v>452</v>
-      </c>
-      <c r="G18" t="s">
-        <v>461</v>
-      </c>
-      <c r="H18" t="s">
-        <v>438</v>
-      </c>
-      <c r="I18" t="s">
-        <v>462</v>
-      </c>
-      <c r="J18" t="s">
-        <v>447</v>
-      </c>
-      <c r="K18" t="s">
-        <v>463</v>
-      </c>
-      <c r="L18" t="s">
-        <v>464</v>
-      </c>
-      <c r="M18" t="s">
-        <v>465</v>
-      </c>
-      <c r="N18" t="s">
-        <v>249</v>
-      </c>
-      <c r="O18" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>466</v>
-      </c>
-      <c r="B19" t="s">
-        <v>467</v>
-      </c>
-      <c r="C19" t="s">
-        <v>456</v>
-      </c>
-      <c r="D19" t="s">
-        <v>451</v>
-      </c>
-      <c r="E19" t="s">
-        <v>424</v>
-      </c>
-      <c r="F19" t="s">
-        <v>447</v>
-      </c>
-      <c r="G19" t="s">
-        <v>447</v>
-      </c>
-      <c r="H19" t="s">
-        <v>451</v>
-      </c>
-      <c r="I19" t="s">
-        <v>468</v>
-      </c>
-      <c r="J19" t="s">
-        <v>467</v>
-      </c>
-      <c r="K19" t="s">
-        <v>467</v>
-      </c>
-      <c r="L19" t="s">
-        <v>467</v>
-      </c>
-      <c r="M19" t="s">
-        <v>469</v>
-      </c>
-      <c r="N19" t="s">
-        <v>470</v>
-      </c>
-      <c r="O19" t="s">
-        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -10067,176 +9748,900 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26" customWidth="1"/>
-    <col min="6" max="6" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.140625" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>240</v>
       </c>
       <c r="B1" t="s">
+        <v>332</v>
+      </c>
+      <c r="C1" t="s">
+        <v>438</v>
+      </c>
+      <c r="D1" t="s">
+        <v>439</v>
+      </c>
+      <c r="E1" t="s">
+        <v>359</v>
+      </c>
+      <c r="F1" t="s">
+        <v>364</v>
+      </c>
+      <c r="G1" t="s">
+        <v>368</v>
+      </c>
+      <c r="H1" t="s">
+        <v>372</v>
+      </c>
+      <c r="I1" t="s">
+        <v>320</v>
+      </c>
+      <c r="J1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L1" t="s">
+        <v>308</v>
+      </c>
+      <c r="M1" t="s">
+        <v>311</v>
+      </c>
+      <c r="N1" t="s">
+        <v>314</v>
+      </c>
+      <c r="O1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F2" t="s">
+        <v>249</v>
+      </c>
+      <c r="G2" t="s">
+        <v>249</v>
+      </c>
+      <c r="H2" t="s">
+        <v>249</v>
+      </c>
+      <c r="I2" t="s">
+        <v>249</v>
+      </c>
+      <c r="J2" t="s">
+        <v>249</v>
+      </c>
+      <c r="K2" t="s">
+        <v>249</v>
+      </c>
+      <c r="L2" t="s">
+        <v>249</v>
+      </c>
+      <c r="M2" t="s">
+        <v>249</v>
+      </c>
+      <c r="N2" t="s">
+        <v>249</v>
+      </c>
+      <c r="O2" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>441</v>
+      </c>
+      <c r="B3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E3" t="s">
+        <v>249</v>
+      </c>
+      <c r="F3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G3" t="s">
+        <v>249</v>
+      </c>
+      <c r="H3" t="s">
+        <v>249</v>
+      </c>
+      <c r="I3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J3" t="s">
+        <v>249</v>
+      </c>
+      <c r="K3" t="s">
+        <v>249</v>
+      </c>
+      <c r="L3" t="s">
+        <v>249</v>
+      </c>
+      <c r="M3" t="s">
+        <v>249</v>
+      </c>
+      <c r="N3" t="s">
+        <v>249</v>
+      </c>
+      <c r="O3" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>442</v>
+      </c>
+      <c r="B4" t="s">
+        <v>443</v>
+      </c>
+      <c r="C4" t="s">
+        <v>249</v>
+      </c>
+      <c r="D4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E4" t="s">
+        <v>249</v>
+      </c>
+      <c r="F4" t="s">
+        <v>249</v>
+      </c>
+      <c r="G4" t="s">
+        <v>249</v>
+      </c>
+      <c r="H4" t="s">
+        <v>249</v>
+      </c>
+      <c r="I4" t="s">
+        <v>249</v>
+      </c>
+      <c r="J4" t="s">
+        <v>249</v>
+      </c>
+      <c r="K4" t="s">
+        <v>249</v>
+      </c>
+      <c r="L4" t="s">
+        <v>249</v>
+      </c>
+      <c r="M4" t="s">
+        <v>249</v>
+      </c>
+      <c r="N4" t="s">
+        <v>249</v>
+      </c>
+      <c r="O4" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>444</v>
+      </c>
+      <c r="B5" t="s">
+        <v>445</v>
+      </c>
+      <c r="C5" t="s">
+        <v>446</v>
+      </c>
+      <c r="D5" t="s">
+        <v>249</v>
+      </c>
+      <c r="E5" t="s">
+        <v>249</v>
+      </c>
+      <c r="F5" t="s">
+        <v>249</v>
+      </c>
+      <c r="G5" t="s">
+        <v>249</v>
+      </c>
+      <c r="H5" t="s">
+        <v>249</v>
+      </c>
+      <c r="I5" t="s">
+        <v>249</v>
+      </c>
+      <c r="J5" t="s">
+        <v>249</v>
+      </c>
+      <c r="K5" t="s">
+        <v>249</v>
+      </c>
+      <c r="L5" t="s">
+        <v>249</v>
+      </c>
+      <c r="M5" t="s">
+        <v>249</v>
+      </c>
+      <c r="N5" t="s">
+        <v>249</v>
+      </c>
+      <c r="O5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>447</v>
+      </c>
+      <c r="B6" t="s">
+        <v>249</v>
+      </c>
+      <c r="C6" t="s">
+        <v>249</v>
+      </c>
+      <c r="D6" t="s">
+        <v>249</v>
+      </c>
+      <c r="E6" t="s">
+        <v>249</v>
+      </c>
+      <c r="F6" t="s">
+        <v>249</v>
+      </c>
+      <c r="G6" t="s">
+        <v>249</v>
+      </c>
+      <c r="H6" t="s">
+        <v>249</v>
+      </c>
+      <c r="I6" t="s">
+        <v>249</v>
+      </c>
+      <c r="J6" t="s">
+        <v>249</v>
+      </c>
+      <c r="K6" t="s">
+        <v>249</v>
+      </c>
+      <c r="L6" t="s">
+        <v>249</v>
+      </c>
+      <c r="M6" t="s">
+        <v>249</v>
+      </c>
+      <c r="N6" t="s">
+        <v>249</v>
+      </c>
+      <c r="O6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>448</v>
+      </c>
+      <c r="B7" t="s">
+        <v>449</v>
+      </c>
+      <c r="C7" t="s">
+        <v>450</v>
+      </c>
+      <c r="D7" t="s">
+        <v>451</v>
+      </c>
+      <c r="E7" t="s">
+        <v>249</v>
+      </c>
+      <c r="F7" t="s">
+        <v>249</v>
+      </c>
+      <c r="G7" t="s">
+        <v>249</v>
+      </c>
+      <c r="H7" t="s">
+        <v>249</v>
+      </c>
+      <c r="I7" t="s">
+        <v>249</v>
+      </c>
+      <c r="J7" t="s">
+        <v>249</v>
+      </c>
+      <c r="K7" t="s">
+        <v>249</v>
+      </c>
+      <c r="L7" t="s">
+        <v>249</v>
+      </c>
+      <c r="M7" t="s">
+        <v>249</v>
+      </c>
+      <c r="N7" t="s">
+        <v>249</v>
+      </c>
+      <c r="O7" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>452</v>
+      </c>
+      <c r="B8" t="s">
+        <v>453</v>
+      </c>
+      <c r="C8" t="s">
+        <v>454</v>
+      </c>
+      <c r="D8" t="s">
+        <v>455</v>
+      </c>
+      <c r="E8" t="s">
+        <v>456</v>
+      </c>
+      <c r="F8" t="s">
+        <v>249</v>
+      </c>
+      <c r="G8" t="s">
+        <v>249</v>
+      </c>
+      <c r="H8" t="s">
+        <v>249</v>
+      </c>
+      <c r="I8" t="s">
+        <v>249</v>
+      </c>
+      <c r="J8" t="s">
+        <v>249</v>
+      </c>
+      <c r="K8" t="s">
+        <v>249</v>
+      </c>
+      <c r="L8" t="s">
+        <v>249</v>
+      </c>
+      <c r="M8" t="s">
+        <v>249</v>
+      </c>
+      <c r="N8" t="s">
+        <v>249</v>
+      </c>
+      <c r="O8" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>457</v>
+      </c>
+      <c r="B9" t="s">
+        <v>450</v>
+      </c>
+      <c r="C9" t="s">
+        <v>451</v>
+      </c>
+      <c r="D9" t="s">
+        <v>458</v>
+      </c>
+      <c r="E9" t="s">
+        <v>459</v>
+      </c>
+      <c r="F9" t="s">
+        <v>460</v>
+      </c>
+      <c r="G9" t="s">
+        <v>249</v>
+      </c>
+      <c r="H9" t="s">
+        <v>249</v>
+      </c>
+      <c r="I9" t="s">
+        <v>249</v>
+      </c>
+      <c r="J9" t="s">
+        <v>249</v>
+      </c>
+      <c r="K9" t="s">
+        <v>249</v>
+      </c>
+      <c r="L9" t="s">
+        <v>249</v>
+      </c>
+      <c r="M9" t="s">
+        <v>249</v>
+      </c>
+      <c r="N9" t="s">
+        <v>249</v>
+      </c>
+      <c r="O9" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>461</v>
+      </c>
+      <c r="B10" t="s">
+        <v>462</v>
+      </c>
+      <c r="C10" t="s">
+        <v>463</v>
+      </c>
+      <c r="D10" t="s">
+        <v>443</v>
+      </c>
+      <c r="E10" t="s">
+        <v>464</v>
+      </c>
+      <c r="F10" t="s">
+        <v>465</v>
+      </c>
+      <c r="G10" t="s">
+        <v>466</v>
+      </c>
+      <c r="H10" t="s">
+        <v>249</v>
+      </c>
+      <c r="I10" t="s">
+        <v>249</v>
+      </c>
+      <c r="J10" t="s">
+        <v>249</v>
+      </c>
+      <c r="K10" t="s">
+        <v>249</v>
+      </c>
+      <c r="L10" t="s">
+        <v>249</v>
+      </c>
+      <c r="M10" t="s">
+        <v>249</v>
+      </c>
+      <c r="N10" t="s">
+        <v>249</v>
+      </c>
+      <c r="O10" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>467</v>
+      </c>
+      <c r="B11" t="s">
+        <v>249</v>
+      </c>
+      <c r="C11" t="s">
+        <v>249</v>
+      </c>
+      <c r="D11" t="s">
+        <v>249</v>
+      </c>
+      <c r="E11" t="s">
+        <v>249</v>
+      </c>
+      <c r="F11" t="s">
+        <v>249</v>
+      </c>
+      <c r="G11" t="s">
+        <v>249</v>
+      </c>
+      <c r="H11" t="s">
+        <v>249</v>
+      </c>
+      <c r="I11" t="s">
+        <v>249</v>
+      </c>
+      <c r="J11" t="s">
+        <v>249</v>
+      </c>
+      <c r="K11" t="s">
+        <v>249</v>
+      </c>
+      <c r="L11" t="s">
+        <v>249</v>
+      </c>
+      <c r="M11" t="s">
+        <v>249</v>
+      </c>
+      <c r="N11" t="s">
+        <v>249</v>
+      </c>
+      <c r="O11" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>468</v>
+      </c>
+      <c r="B12" t="s">
+        <v>469</v>
+      </c>
+      <c r="C12" t="s">
+        <v>470</v>
+      </c>
+      <c r="D12" t="s">
+        <v>443</v>
+      </c>
+      <c r="E12" t="s">
+        <v>471</v>
+      </c>
+      <c r="F12" t="s">
+        <v>472</v>
+      </c>
+      <c r="G12" t="s">
         <v>473</v>
       </c>
-      <c r="C1" t="s">
-        <v>472</v>
-      </c>
-      <c r="D1" t="s">
-        <v>471</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="H12" t="s">
+        <v>474</v>
+      </c>
+      <c r="I12" t="s">
+        <v>249</v>
+      </c>
+      <c r="J12" t="s">
+        <v>249</v>
+      </c>
+      <c r="K12" t="s">
+        <v>249</v>
+      </c>
+      <c r="L12" t="s">
+        <v>249</v>
+      </c>
+      <c r="M12" t="s">
+        <v>249</v>
+      </c>
+      <c r="N12" t="s">
+        <v>249</v>
+      </c>
+      <c r="O12" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>475</v>
+      </c>
+      <c r="B13" t="s">
+        <v>249</v>
+      </c>
+      <c r="C13" t="s">
+        <v>249</v>
+      </c>
+      <c r="D13" t="s">
+        <v>249</v>
+      </c>
+      <c r="E13" t="s">
+        <v>249</v>
+      </c>
+      <c r="F13" t="s">
+        <v>249</v>
+      </c>
+      <c r="G13" t="s">
+        <v>249</v>
+      </c>
+      <c r="H13" t="s">
+        <v>249</v>
+      </c>
+      <c r="I13" t="s">
+        <v>249</v>
+      </c>
+      <c r="J13" t="s">
+        <v>249</v>
+      </c>
+      <c r="K13" t="s">
+        <v>249</v>
+      </c>
+      <c r="L13" t="s">
+        <v>249</v>
+      </c>
+      <c r="M13" t="s">
+        <v>249</v>
+      </c>
+      <c r="N13" t="s">
+        <v>249</v>
+      </c>
+      <c r="O13" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>476</v>
       </c>
-      <c r="F1" t="s">
-        <v>475</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="B14" t="s">
+        <v>477</v>
+      </c>
+      <c r="C14" t="s">
+        <v>478</v>
+      </c>
+      <c r="D14" t="s">
+        <v>458</v>
+      </c>
+      <c r="E14" t="s">
+        <v>453</v>
+      </c>
+      <c r="F14" t="s">
+        <v>462</v>
+      </c>
+      <c r="G14" t="s">
+        <v>445</v>
+      </c>
+      <c r="H14" t="s">
+        <v>464</v>
+      </c>
+      <c r="I14" t="s">
+        <v>479</v>
+      </c>
+      <c r="J14" t="s">
+        <v>249</v>
+      </c>
+      <c r="K14" t="s">
+        <v>249</v>
+      </c>
+      <c r="L14" t="s">
+        <v>249</v>
+      </c>
+      <c r="M14" t="s">
+        <v>249</v>
+      </c>
+      <c r="N14" t="s">
+        <v>249</v>
+      </c>
+      <c r="O14" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>480</v>
+      </c>
+      <c r="B15" t="s">
+        <v>481</v>
+      </c>
+      <c r="C15" t="s">
+        <v>482</v>
+      </c>
+      <c r="D15" t="s">
+        <v>478</v>
+      </c>
+      <c r="E15" t="s">
+        <v>483</v>
+      </c>
+      <c r="F15" t="s">
+        <v>484</v>
+      </c>
+      <c r="G15" t="s">
+        <v>443</v>
+      </c>
+      <c r="H15" t="s">
+        <v>469</v>
+      </c>
+      <c r="I15" t="s">
+        <v>453</v>
+      </c>
+      <c r="J15" t="s">
+        <v>466</v>
+      </c>
+      <c r="K15" t="s">
+        <v>249</v>
+      </c>
+      <c r="L15" t="s">
+        <v>249</v>
+      </c>
+      <c r="M15" t="s">
+        <v>249</v>
+      </c>
+      <c r="N15" t="s">
+        <v>249</v>
+      </c>
+      <c r="O15" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>485</v>
+      </c>
+      <c r="B16" t="s">
+        <v>453</v>
+      </c>
+      <c r="C16" t="s">
+        <v>458</v>
+      </c>
+      <c r="D16" t="s">
+        <v>443</v>
+      </c>
+      <c r="E16" t="s">
+        <v>486</v>
+      </c>
+      <c r="F16" t="s">
+        <v>455</v>
+      </c>
+      <c r="G16" t="s">
+        <v>486</v>
+      </c>
+      <c r="H16" t="s">
+        <v>464</v>
+      </c>
+      <c r="I16" t="s">
+        <v>450</v>
+      </c>
+      <c r="J16" t="s">
+        <v>483</v>
+      </c>
+      <c r="K16" t="s">
+        <v>478</v>
+      </c>
+      <c r="L16" t="s">
+        <v>249</v>
+      </c>
+      <c r="M16" t="s">
+        <v>249</v>
+      </c>
+      <c r="N16" t="s">
+        <v>249</v>
+      </c>
+      <c r="O16" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>487</v>
+      </c>
+      <c r="B17" t="s">
+        <v>488</v>
+      </c>
+      <c r="C17" t="s">
+        <v>489</v>
+      </c>
+      <c r="D17" t="s">
+        <v>469</v>
+      </c>
+      <c r="E17" t="s">
+        <v>450</v>
+      </c>
+      <c r="F17" t="s">
+        <v>458</v>
+      </c>
+      <c r="G17" t="s">
+        <v>443</v>
+      </c>
+      <c r="H17" t="s">
+        <v>453</v>
+      </c>
+      <c r="I17" t="s">
+        <v>484</v>
+      </c>
+      <c r="J17" t="s">
+        <v>490</v>
+      </c>
+      <c r="K17" t="s">
+        <v>469</v>
+      </c>
+      <c r="L17" t="s">
+        <v>469</v>
+      </c>
+      <c r="M17" t="s">
+        <v>249</v>
+      </c>
+      <c r="N17" t="s">
+        <v>249</v>
+      </c>
+      <c r="O17" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>491</v>
+      </c>
+      <c r="B18" t="s">
+        <v>479</v>
+      </c>
+      <c r="C18" t="s">
+        <v>489</v>
+      </c>
+      <c r="D18" t="s">
+        <v>479</v>
+      </c>
+      <c r="E18" t="s">
+        <v>492</v>
+      </c>
+      <c r="F18" t="s">
+        <v>493</v>
+      </c>
+      <c r="G18" t="s">
+        <v>494</v>
+      </c>
+      <c r="H18" t="s">
+        <v>488</v>
+      </c>
+      <c r="I18" t="s">
+        <v>495</v>
+      </c>
+      <c r="J18" t="s">
+        <v>449</v>
+      </c>
+      <c r="K18" t="s">
+        <v>481</v>
+      </c>
+      <c r="L18" t="s">
+        <v>496</v>
+      </c>
+      <c r="M18" t="s">
+        <v>497</v>
+      </c>
+      <c r="N18" t="s">
+        <v>249</v>
+      </c>
+      <c r="O18" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>498</v>
+      </c>
+      <c r="B19" t="s">
+        <v>478</v>
+      </c>
+      <c r="C19" t="s">
+        <v>450</v>
+      </c>
+      <c r="D19" t="s">
+        <v>462</v>
+      </c>
+      <c r="E19" t="s">
+        <v>443</v>
+      </c>
+      <c r="F19" t="s">
+        <v>478</v>
+      </c>
+      <c r="G19" t="s">
+        <v>479</v>
+      </c>
+      <c r="H19" t="s">
+        <v>482</v>
+      </c>
+      <c r="I19" t="s">
+        <v>499</v>
+      </c>
+      <c r="J19" t="s">
+        <v>492</v>
+      </c>
+      <c r="K19" t="s">
+        <v>492</v>
+      </c>
+      <c r="L19" t="s">
+        <v>492</v>
+      </c>
+      <c r="M19" t="s">
         <v>474</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>479</v>
-      </c>
-      <c r="C2" t="s">
-        <v>478</v>
-      </c>
-      <c r="D2" t="s">
-        <v>477</v>
-      </c>
-      <c r="E2" t="s">
-        <v>482</v>
-      </c>
-      <c r="F2" t="s">
-        <v>481</v>
-      </c>
-      <c r="G2" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>483</v>
-      </c>
-      <c r="B3" t="s">
-        <v>486</v>
-      </c>
-      <c r="C3" t="s">
-        <v>485</v>
-      </c>
-      <c r="D3" t="s">
-        <v>484</v>
-      </c>
-      <c r="E3" t="s">
-        <v>487</v>
-      </c>
-      <c r="F3" t="s">
-        <v>488</v>
-      </c>
-      <c r="G3" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>308</v>
-      </c>
-      <c r="B4" t="s">
-        <v>491</v>
-      </c>
-      <c r="C4" t="s">
-        <v>490</v>
-      </c>
-      <c r="D4" t="s">
-        <v>489</v>
-      </c>
-      <c r="E4" t="s">
-        <v>494</v>
-      </c>
-      <c r="F4" t="s">
-        <v>493</v>
-      </c>
-      <c r="G4" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>311</v>
-      </c>
-      <c r="B5" t="s">
-        <v>497</v>
-      </c>
-      <c r="C5" t="s">
-        <v>496</v>
-      </c>
-      <c r="D5" t="s">
-        <v>495</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="N19" t="s">
         <v>500</v>
       </c>
-      <c r="F5" t="s">
-        <v>499</v>
-      </c>
-      <c r="G5" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>314</v>
-      </c>
-      <c r="B6" t="s">
-        <v>503</v>
-      </c>
-      <c r="C6" t="s">
-        <v>502</v>
-      </c>
-      <c r="D6" t="s">
-        <v>501</v>
-      </c>
-      <c r="E6" t="s">
-        <v>506</v>
-      </c>
-      <c r="F6" t="s">
-        <v>505</v>
-      </c>
-      <c r="G6" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>317</v>
-      </c>
-      <c r="B7" t="s">
-        <v>509</v>
-      </c>
-      <c r="C7" t="s">
-        <v>508</v>
-      </c>
-      <c r="D7" t="s">
-        <v>507</v>
-      </c>
-      <c r="E7" t="s">
-        <v>512</v>
-      </c>
-      <c r="F7" t="s">
-        <v>511</v>
-      </c>
-      <c r="G7" t="s">
-        <v>510</v>
+      <c r="O19" t="s">
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -10251,118 +10656,133 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>513</v>
+        <v>240</v>
       </c>
       <c r="B1" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="C1" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="D1" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="E1" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="F1" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>505</v>
+      </c>
+      <c r="G1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>408</v>
+        <v>507</v>
       </c>
       <c r="C2" t="s">
-        <v>278</v>
+        <v>508</v>
       </c>
       <c r="D2" t="s">
+        <v>509</v>
+      </c>
+      <c r="E2" t="s">
+        <v>510</v>
+      </c>
+      <c r="F2" t="s">
+        <v>511</v>
+      </c>
+      <c r="G2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>513</v>
+      </c>
+      <c r="B3" t="s">
+        <v>514</v>
+      </c>
+      <c r="C3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D3" t="s">
+        <v>516</v>
+      </c>
+      <c r="E3" t="s">
+        <v>517</v>
+      </c>
+      <c r="F3" t="s">
+        <v>518</v>
+      </c>
+      <c r="G3" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B4" t="s">
         <v>519</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C4" t="s">
         <v>520</v>
       </c>
-      <c r="F2" t="s">
+      <c r="D4" t="s">
         <v>521</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="E4" t="s">
         <v>522</v>
       </c>
-      <c r="C3" t="s">
-        <v>277</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="F4" t="s">
         <v>523</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G4" t="s">
         <v>524</v>
       </c>
-      <c r="F3" t="s">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B5" t="s">
         <v>525</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="C5" t="s">
         <v>526</v>
       </c>
-      <c r="C4" t="s">
-        <v>277</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="D5" t="s">
         <v>527</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E5" t="s">
         <v>528</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F5" t="s">
         <v>529</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>483</v>
-      </c>
-      <c r="B5" t="s">
-        <v>408</v>
-      </c>
-      <c r="C5" t="s">
-        <v>278</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="G5" t="s">
         <v>530</v>
       </c>
-      <c r="E5" t="s">
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>314</v>
+      </c>
+      <c r="B6" t="s">
         <v>531</v>
       </c>
-      <c r="F5" t="s">
+      <c r="C6" t="s">
         <v>532</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>483</v>
-      </c>
-      <c r="B6" t="s">
-        <v>522</v>
-      </c>
-      <c r="C6" t="s">
-        <v>277</v>
       </c>
       <c r="D6" t="s">
         <v>533</v>
@@ -10371,267 +10791,33 @@
         <v>534</v>
       </c>
       <c r="F6" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>535</v>
+      </c>
+      <c r="G6" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>483</v>
+        <v>317</v>
       </c>
       <c r="B7" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="C7" t="s">
-        <v>277</v>
+        <v>538</v>
       </c>
       <c r="D7" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="E7" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="F7" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>308</v>
-      </c>
-      <c r="B8" t="s">
-        <v>408</v>
-      </c>
-      <c r="C8" t="s">
-        <v>278</v>
-      </c>
-      <c r="D8" t="s">
-        <v>529</v>
-      </c>
-      <c r="E8" t="s">
-        <v>537</v>
-      </c>
-      <c r="F8" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>308</v>
-      </c>
-      <c r="B9" t="s">
-        <v>522</v>
-      </c>
-      <c r="C9" t="s">
-        <v>277</v>
-      </c>
-      <c r="D9" t="s">
-        <v>539</v>
-      </c>
-      <c r="E9" t="s">
-        <v>540</v>
-      </c>
-      <c r="F9" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>308</v>
-      </c>
-      <c r="B10" t="s">
-        <v>526</v>
-      </c>
-      <c r="C10" t="s">
-        <v>277</v>
-      </c>
-      <c r="D10" t="s">
         <v>541</v>
       </c>
-      <c r="E10" t="s">
+      <c r="G7" t="s">
         <v>542</v>
-      </c>
-      <c r="F10" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>311</v>
-      </c>
-      <c r="B11" t="s">
-        <v>408</v>
-      </c>
-      <c r="C11" t="s">
-        <v>278</v>
-      </c>
-      <c r="D11" t="s">
-        <v>543</v>
-      </c>
-      <c r="E11" t="s">
-        <v>544</v>
-      </c>
-      <c r="F11" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>311</v>
-      </c>
-      <c r="B12" t="s">
-        <v>522</v>
-      </c>
-      <c r="C12" t="s">
-        <v>277</v>
-      </c>
-      <c r="D12" t="s">
-        <v>545</v>
-      </c>
-      <c r="E12" t="s">
-        <v>546</v>
-      </c>
-      <c r="F12" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>311</v>
-      </c>
-      <c r="B13" t="s">
-        <v>526</v>
-      </c>
-      <c r="C13" t="s">
-        <v>277</v>
-      </c>
-      <c r="D13" t="s">
-        <v>547</v>
-      </c>
-      <c r="E13" t="s">
-        <v>548</v>
-      </c>
-      <c r="F13" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>314</v>
-      </c>
-      <c r="B14" t="s">
-        <v>408</v>
-      </c>
-      <c r="C14" t="s">
-        <v>278</v>
-      </c>
-      <c r="D14" t="s">
-        <v>545</v>
-      </c>
-      <c r="E14" t="s">
-        <v>549</v>
-      </c>
-      <c r="F14" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>314</v>
-      </c>
-      <c r="B15" t="s">
-        <v>522</v>
-      </c>
-      <c r="C15" t="s">
-        <v>277</v>
-      </c>
-      <c r="D15" t="s">
-        <v>550</v>
-      </c>
-      <c r="E15" t="s">
-        <v>551</v>
-      </c>
-      <c r="F15" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>314</v>
-      </c>
-      <c r="B16" t="s">
-        <v>526</v>
-      </c>
-      <c r="C16" t="s">
-        <v>277</v>
-      </c>
-      <c r="D16" t="s">
-        <v>552</v>
-      </c>
-      <c r="E16" t="s">
-        <v>553</v>
-      </c>
-      <c r="F16" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>317</v>
-      </c>
-      <c r="B17" t="s">
-        <v>408</v>
-      </c>
-      <c r="C17" t="s">
-        <v>278</v>
-      </c>
-      <c r="D17" t="s">
-        <v>554</v>
-      </c>
-      <c r="E17" t="s">
-        <v>548</v>
-      </c>
-      <c r="F17" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>317</v>
-      </c>
-      <c r="B18" t="s">
-        <v>522</v>
-      </c>
-      <c r="C18" t="s">
-        <v>277</v>
-      </c>
-      <c r="D18" t="s">
-        <v>555</v>
-      </c>
-      <c r="E18" t="s">
-        <v>556</v>
-      </c>
-      <c r="F18" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>317</v>
-      </c>
-      <c r="B19" t="s">
-        <v>526</v>
-      </c>
-      <c r="C19" t="s">
-        <v>277</v>
-      </c>
-      <c r="D19" t="s">
-        <v>557</v>
-      </c>
-      <c r="E19" t="s">
-        <v>542</v>
-      </c>
-      <c r="F19" t="s">
-        <v>521</v>
       </c>
     </row>
   </sheetData>
